--- a/光伏配储项目/电价数据/2026/德城站.xlsx
+++ b/光伏配储项目/电价数据/2026/德城站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38557</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7411</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5709099999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.57339</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.4978</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.49312</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43754</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42306</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40198</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42307</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41693</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42063</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.4128500000000001</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30001</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.11252</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.09173000000000001</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.08331999999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.10728</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.0429</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.08505</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.10145</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.1026</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.08393</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08946999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.0723</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.05175</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00344</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14799</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21478</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24157</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.20218</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.07442</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00073</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.26689</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.17928</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.27922</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51898</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.37559</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.46468</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.8300700000000001</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43008</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5641799999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43971</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.58947</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7918500000000001</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.63426</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.60397</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7114299999999999</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.78342</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.65484</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.60573</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.6376900000000001</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5841499999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.57578</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.63071</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6005199999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48574</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42563</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.62978</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.76054</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.1604</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.81937</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.52577</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50544</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49099</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4706</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39151</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41984</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.50237</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.59833</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.68088</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40417</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5010599999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.14753</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.75748</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.8835599999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7417</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.47817</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.10204</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.28175</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.45991</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.2597</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.30952</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.24439</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.45384</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.5288099999999999</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.65107</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.68511</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7493</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.75662</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.48638</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8067300000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.48509</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.39812</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8819900000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59324</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44002</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43367</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37846</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33453</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5258700000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48131</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39459</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43363</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44983</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38436</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47389</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44973</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36931</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34868</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.19183</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.26579</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.49821</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.46966</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.14291</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.24573</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.29466</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.27608</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.37878</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.40545</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.3947</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.49979</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.50093</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.58785</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.49203</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.58809</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.44093</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.39194</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.43225</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.44821</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.40619</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.38973</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34256</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.40181</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46025</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30709</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38951</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.36687</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.1396</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.2002</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.15189</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.21221</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40776</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.05579</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.11323</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.28565</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.15137</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.49003</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.05061</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.11732</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.20808</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.23178</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.22958</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.24673</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27504</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.1474</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.55538</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45264</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.44282</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31086</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29675</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29865</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37107</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30932</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.29412</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29026</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29033</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32448</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2794700000000001</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04578</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04647</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04581</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04628</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04413</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04818</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04855</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04848</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.03552</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04758</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04497</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04022999999999999</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04062</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.0411</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.03915999999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04251</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04178</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04205</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04306</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04349</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04206</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.0457</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04839</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05413</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05575</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00028</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.15215</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04395</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.1039</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.29003</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34135</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41741</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35525</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35113</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6693</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42389</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04599</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04363</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03299000000000001</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04228</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10605</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>-0.00043</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03886999999999999</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04747</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04307</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.0435</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04542</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04328</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.0429</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04129</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04513</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04496</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04511</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04317</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04389</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04078</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.0428</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04445</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04995</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04722999999999999</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04754</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20032</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14313</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29054</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33595</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31836</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40516</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29508</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2716</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17271</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17133</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14803</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15976</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15896</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23674</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21437</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22691</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28621</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29121</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28139</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28148</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28098</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28135</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32296</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3161</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42712</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41706</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41386</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38509</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50764</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92032</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91722</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8724400000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30128</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.36298</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.89675</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63317</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.19618</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87324</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5497000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.34017</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03931</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.54013</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79892</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53086</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78096</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78387</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87775</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87803</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50061</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.40596</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.40952</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21662</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87917</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55123</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63139</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54072</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50046</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42541</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43886</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45284</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40011</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43399</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34093</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40541</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35233</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45092</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58733</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42822</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5962999999999999</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60239</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66872</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.57782</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87636</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63449</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.8550800000000001</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83696</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8602799999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44006</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31026</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35742</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31556</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31562</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41309</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45294</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39189</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35352</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.93388</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4704100000000001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.49841</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.37376</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38914</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50076</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37093</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3581</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36323</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29068</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16498</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19944</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.20729</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27729</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31327</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25561</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32386</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38584</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43621</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.31256</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42324</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44861</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42078</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40208</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59787</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8904099999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.3192</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.12625</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6929500000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7811399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6445</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.57662</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.44806</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.49623</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41067</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42121</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43134</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41119</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43092</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.44775</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42099</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43176</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41064</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42143</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30369</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.01779</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.56209</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.37064</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.55176</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29618</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.16709</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26262</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28631</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37495</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36302</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.5762200000000001</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46082</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.75948</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46179</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43782</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42337</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32922</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32451</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42137</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34889</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.28819</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23332</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15224</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28855</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15967</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14673</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14425</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14657</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14481</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26547</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.27445</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14727</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.12666</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11586</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.10795</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14291</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14322</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40059</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44236</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43763</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43696</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44156</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34805</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34923</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5355700000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46514</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42122</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41345</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37833</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3911</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37891</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.38955</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34656</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34003</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29454</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28925</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.26113</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.19454</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2468</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.23827</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.28449</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23797</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28113</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32491</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35722</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2578</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36696</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37238</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.35998</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38412</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33839</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43219</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.36742</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.00521</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.2844</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25055</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.08902</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.21419</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.25353</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71111</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32574</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51528</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2747</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.38615</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.29108</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29953</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.37278</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40482</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35503</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38723</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37925</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34968</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35344</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36591</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35482</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34355</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.36489</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38097</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38458</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43809</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.68265</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.78095</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47571</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39232</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34387</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34943</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41665</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36236</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35311</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35221</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37073</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3564</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.3883</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38187</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14661</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28402</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19891</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25722</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27996</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21827</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26195</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27816</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3052</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14994</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33041</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35936</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31698</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6114700000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6569299999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6831199999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.48906</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7379</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.88381</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.46971</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48252</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48351</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37483</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36013</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49118</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.55611</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.50166</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3859</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41895</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38832</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40175</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41422</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40344</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44678</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45594</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5611</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49538</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44696</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.5717300000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4633</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44215</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38854</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38899</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42365</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4557</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33666</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.40218</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.28811</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.64063</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.28093</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.43325</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48781</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50895</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.53949</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.60741</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.77906</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.79611</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.92231</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.7094</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80372</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.59962</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.55283</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.92248</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.84621</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62982</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.70457</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.45231</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.47166</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47824</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.49229</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.56492</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42882</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44349</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46815</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45362</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.43229</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43138</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46912</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39833</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37867</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37371</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38674</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40378</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1819</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40535</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39057</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4643</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.11065</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18097</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29512</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35286</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.37318</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.41581</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41244</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38183</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38466</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34555</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36375</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.3656</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33017</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39297</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35866</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27096</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22834</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28863</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23068</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28866</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25044</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25321</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13972</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29958</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24989</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04335</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25169</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16904</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18085</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27258</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3094</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22782</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26172</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23185</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28269</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35208</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3729</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35065</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32389</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31896</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.30918</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29087</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.2626</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17124</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21132</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01784</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00028</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02742</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04972</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.10867</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01415</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03972</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02204</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.0444</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04263</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04894</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02692</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0324</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04975</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.11903</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00275</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04978</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04974</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03298</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04289</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17091</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20199</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26791</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.26951</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.26857</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.1543</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.59121</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.18108</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.30075</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.25758</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24836</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26313</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.23221</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.27738</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28414</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.23825</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.1783</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.65515</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6585</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.67091</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.59261</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.17256</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09298000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.24236</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.18629</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.13554</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.14175</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.09959999999999999</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23158</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12446</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04859</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.11404</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.1835</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02456</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.13386</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.13896</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.15844</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.01191</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.11725</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.12307</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.12435</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.15457</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.37611</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3951</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37087</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32382</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32805</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.07112</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.48072</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.37493</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.41576</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32417</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29196</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.46242</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.45933</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.44015</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13946</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27006</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31224</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37564</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33329</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.28684</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33755</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35933</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35194</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.5898300000000001</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.5309400000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26063</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28328</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41488</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3982</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.5065</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5203300000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45403</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46594</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.38352</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.42893</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.38734</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37325</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.48111</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38942</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.51911</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.37516</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37536</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37419</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36902</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35976</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35617</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34721</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4095299999999999</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36975</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.40379</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3717200000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43148</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37755</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26504</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35423</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30933</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34623</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.46651</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.44574</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42733</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42708</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.5122000000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.59729</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.59513</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46152</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.57973</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.51307</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.56172</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.5256900000000001</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.4070299999999999</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.56899</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.51855</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.99438</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.87448</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.6047899999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.59911</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.40808</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.46084</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.38061</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37771</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37962</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27031</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33885</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35155</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.24366</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.27223</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.28504</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.12679</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.21423</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.17979</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05606000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.28985</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.13498</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.02447</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.19446</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16281</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.00331</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29537</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25549</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.15404</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.05213</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04809</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.06157</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.14657</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.06952</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.05255</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16948</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.13832</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.16346</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.26197</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.29944</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.28264</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.26096</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35612</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39218</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42459</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.4258</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.44611</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38897</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.52904</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3806</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.97114</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36818</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36175</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36086</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36436</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36651</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31352</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.27505</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.11441</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.01808</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.01821</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.17424</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03997999999999999</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00588</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04563</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01473</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01354</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01466</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.16185</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.26233</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.04437</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.2444</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.1604</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.25624</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.30589</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30968</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.35778</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.48071</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41637</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40612</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5565099999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.58592</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38641</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35489</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38537</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36322</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37542</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38716</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38016</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34962</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34719</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.26253</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.23608</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.14714</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.21364</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24075</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.15517</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04672</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.03304</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04697</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.04772999999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.04657</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.04682</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04448</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.04179</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.0808</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.02892</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06487999999999999</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.09969</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.17616</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20077</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12379</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26804</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.23565</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.12685</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04844</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.26713</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1195</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.24052</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19211</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.21002</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25233</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37136</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37983</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41274</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50979</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4015</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41134</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41231</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40452</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38402</v>
       </c>
     </row>
   </sheetData>
